--- a/VT_REG1_PRI_V12.xlsx
+++ b/VT_REG1_PRI_V12.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC7D0A4-E842-4855-B3A0-AB9988C6CED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC8CCD9-4757-49E6-AA25-CD5BF4B4A33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
